--- a/self_dataset/compare_results/re-entrancy.xlsx
+++ b/self_dataset/compare_results/re-entrancy.xlsx
@@ -420,13 +420,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>buggy_2_CareerOnToken.txt</t>
+          <t>buggy_11_ForTheBlockchain.txt</t>
         </is>
       </c>
     </row>
@@ -474,10 +474,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
         <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -485,376 +485,1454 @@
         <v>107</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>114</v>
-      </c>
-      <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>buggy_11_Owned.txt</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>buggy_3_CareerOnToken.txt</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="A10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>114</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buggy_14_ERC20.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>101</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>105</v>
       </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>107</v>
       </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>110</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>114</v>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>buggy_4_PHO.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="B18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>114</v>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>buggy_14_SaveWon.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>105</v>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>107</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114</v>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>buggy_16_ExclusivePlatform.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>101</v>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>105</v>
       </c>
-      <c r="B20" t="n">
-        <v>6</v>
-      </c>
-      <c r="C20" t="n">
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" t="n">
         <v>2</v>
       </c>
-      <c r="D20" t="n">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>107</v>
       </c>
-      <c r="B21" t="n">
-        <v>11</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>114</v>
-      </c>
-      <c r="B22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" t="n">
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>buggy_6_ChannelWallet.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>105</v>
-      </c>
-      <c r="B26" t="n">
-        <v>8</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>107</v>
-      </c>
-      <c r="B27" t="n">
-        <v>13</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>114</v>
-      </c>
-      <c r="B28" t="n">
-        <v>12</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>buggy_7_AccountWallet.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="D31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>114</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>buggy_17_AZT.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>101</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
         <v>105</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="n">
         <v>8</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>107</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>110</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>114</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>buggy_18__Yesbuzz.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>101</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>105</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>107</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>114</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>buggy_18_Owned.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>101</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>105</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>107</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>114</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>buggy_19_ethBank.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>101</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>105</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>107</v>
+      </c>
+      <c r="B60" t="n">
+        <v>9</v>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>114</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>buggy_1_HotDollarsToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>105</v>
+      </c>
+      <c r="B65" t="n">
+        <v>6</v>
+      </c>
+      <c r="C65" t="n">
+        <v>6</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>107</v>
+      </c>
+      <c r="B66" t="n">
+        <v>11</v>
+      </c>
+      <c r="C66" t="n">
+        <v>11</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>114</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7</v>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>buggy_20_Stoppable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>107</v>
+      </c>
+      <c r="B71" t="n">
+        <v>12</v>
+      </c>
+      <c r="C71" t="n">
+        <v>12</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>114</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>buggy_2_CareerOnToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>105</v>
+      </c>
+      <c r="B76" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>107</v>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" t="n">
+        <v>9</v>
+      </c>
+      <c r="D77" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>110</v>
+      </c>
+      <c r="B78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" t="n">
+        <v>5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>114</v>
+      </c>
+      <c r="B79" t="n">
+        <v>4</v>
+      </c>
+      <c r="C79" t="n">
+        <v>6</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>buggy_3_CareerOnToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>105</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>107</v>
+      </c>
+      <c r="B84" t="n">
+        <v>4</v>
+      </c>
+      <c r="C84" t="n">
+        <v>8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>110</v>
+      </c>
+      <c r="B85" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>114</v>
+      </c>
+      <c r="B86" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="n">
+        <v>6</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>buggy_4_PHO.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>105</v>
+      </c>
+      <c r="B90" t="n">
+        <v>6</v>
+      </c>
+      <c r="C90" t="n">
+        <v>6</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>107</v>
+      </c>
+      <c r="B91" t="n">
+        <v>11</v>
+      </c>
+      <c r="C91" t="n">
+        <v>11</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>114</v>
+      </c>
+      <c r="B92" t="n">
+        <v>7</v>
+      </c>
+      <c r="C92" t="n">
+        <v>7</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>buggy_5_Ownable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>107</v>
+      </c>
+      <c r="B96" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" t="n">
+        <v>7</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>114</v>
+      </c>
+      <c r="B97" t="n">
+        <v>3</v>
+      </c>
+      <c r="C97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>buggy_6_ChannelWallet.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>105</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8</v>
+      </c>
+      <c r="C101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>107</v>
+      </c>
+      <c r="B102" t="n">
         <v>13</v>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="C102" t="n">
+        <v>9</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
         <v>114</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B103" t="n">
         <v>12</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-12</v>
+      <c r="C103" t="n">
+        <v>10</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>buggy_7_AccountWallet.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>101</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>105</v>
+      </c>
+      <c r="B108" t="n">
+        <v>8</v>
+      </c>
+      <c r="C108" t="n">
+        <v>8</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>15</v>
+      </c>
+      <c r="C109" t="n">
+        <v>12</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>114</v>
+      </c>
+      <c r="B110" t="n">
+        <v>13</v>
+      </c>
+      <c r="C110" t="n">
+        <v>11</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>buggy_8_Ownable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>107</v>
+      </c>
+      <c r="B114" t="n">
+        <v>7</v>
+      </c>
+      <c r="C114" t="n">
+        <v>7</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>buggy_9_XLToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>101</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>105</v>
+      </c>
+      <c r="B120" t="n">
+        <v>6</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>107</v>
+      </c>
+      <c r="B121" t="n">
+        <v>15</v>
+      </c>
+      <c r="C121" t="n">
+        <v>9</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>110</v>
+      </c>
+      <c r="B122" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>114</v>
+      </c>
+      <c r="B123" t="n">
+        <v>8</v>
+      </c>
+      <c r="C123" t="n">
+        <v>7</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="19">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A49:D49"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
